--- a/processed_ruby_restored_xlsx/sc226_瑠璃８：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc226_瑠璃８：遊園地.ss.xlsx
@@ -901,7 +901,8 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan glanced up at me with an upturned gaze.</t>
+          <t>Rurichiyo-chan glanced up at me with an upturned
+gaze.</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1101,8 +1102,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>When I let out a lighter laugh, Rurichiyo-chan returns
-a bright smile.</t>
+          <t>When I let out a lighter laugh, Rurichiyo-chan
+returns a bright smile.</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1271,8 +1272,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Mount it, and in an instant anyone can become the hero
-— and the heroine — of a fairy tale.</t>
+          <t>Mount it, and in an instant anyone can become the
+hero — and the heroine — of a fairy tale.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1287,8 +1288,8 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Back then, what was I longing for…? I find myself lost
-in that kind of musing.</t>
+          <t>Back then, what was I longing for…? I find myself
+lost in that kind of musing.</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1592,8 +1593,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>If it'll make Rurichiyo-chan happy, I'll even play the
-part of the prince…！</t>
+          <t>If it'll make Rurichiyo-chan happy, I'll even play
+the part of the prince…！</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1916,7 +1917,8 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>I listened to Rurichiyo-chan's words and nodded again.</t>
+          <t>I listened to Rurichiyo-chan's words and nodded
+again.</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2006,8 +2008,9 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan cast her eyes about as if searching for
-words, repeating the opening and closing of her eyes.</t>
+          <t>Rurichiyo-chan cast her eyes about as if searching
+for words, repeating the opening and closing of her
+eyes.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2022,7 +2025,8 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>Apparently, someone actually took my mutter seriously.</t>
+          <t>Apparently, someone actually took my mutter
+seriously.</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2320,8 +2324,8 @@
       <c r="B121" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan stares back and forth between my face
-and the merry-go-round that's started to spin, quietly
-flustered.</t>
+and the merry-go-round that's started to spin,
+quietly flustered.</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2552,8 +2556,9 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Besides, even I thought that, for once, Rurichiyo-chan
-might refuse, so my happiness is all the greater.</t>
+          <t>Besides, even I thought that, for once,
+Rurichiyo-chan might refuse, so my happiness is all
+the greater.</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3533,8 +3538,8 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan exhales shyly, but little by little she
-gets into it and becomes more disheveled.</t>
+          <t>Rurichiyo-chan exhales shyly, but little by little
+she gets into it and becomes more disheveled.</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3704,8 +3709,8 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>Every time a soft sigh escapes, my penis pulses harder
-and harder.</t>
+          <t>Every time a soft sigh escapes, my penis pulses
+harder and harder.</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3891,8 +3896,8 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>「Aah... fwah！ O-Oji-sama, if you don't hold me... nnh,
-ugh！」</t>
+          <t>「Aah... fwah！ O-Oji-sama, if you don't hold me...
+nnh, ugh！」</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -4062,8 +4067,9 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>「Don't call them 'boobs'... nn！ Nn... Oji-sama, you're
-the one doing something that'll be found out...！」</t>
+          <t>「Don't call them 'boobs'... nn！ Nn... Oji-sama,
+you're the one doing something that'll be found
+out...！」</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4078,8 +4084,9 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>As I stroked Rurichiyo-chan's chest and shook her body
-up and down, down there started getting a little damp.</t>
+          <t>As I stroked Rurichiyo-chan's chest and shook her
+body up and down, down there started getting a little
+damp.</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4109,8 +4116,8 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>「Oji-saama... my body is getting hot... te！ Fwah... I,
-nnf...！」</t>
+          <t>「Oji-saama... my body is getting hot... te！ Fwah...
+I, nnf...！」</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4309,8 +4316,8 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>...Even though the Merrygoround hasn't started yet, we
-two are already getting hyped up by ourselves.</t>
+          <t>...Even though the Merrygoround hasn't started yet,
+we two are already getting hyped up by ourselves.</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4583,8 +4590,8 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>And on top of that, Rurichiyo-chan is lifting her hips
-for me…！</t>
+          <t>And on top of that, Rurichiyo-chan is lifting her
+hips for me…！</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4920,7 +4927,8 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>「Nng！ It's going in... deeper than I thought, huh...！」</t>
+          <t>「Nng！ It's going in... deeper than I thought,
+huh...！」</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -5241,8 +5249,8 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>I have to properly take the lead for the princess, who
-must be startled by the sudden insertion...</t>
+          <t>I have to properly take the lead for the princess,
+who must be startled by the sudden insertion...</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5904,8 +5912,8 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>「Ah... it's okay, I'm feeling Rurichiyo... I'm feeling
-her, ahhh」</t>
+          <t>「Ah... it's okay, I'm feeling Rurichiyo... I'm
+feeling her, ahhh」</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6057,8 +6065,8 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>「Ahfuu... fa, haa...! You... nnngh! Between my legs...
-it feels so, nngh, haa...!」</t>
+          <t>「Ahfuu... fa, haa...! You... nnngh! Between my
+legs... it feels so, nngh, haa...!」</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6119,8 +6127,8 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>It's true that it feels good and that I'm flushed, but
-I don't have any room left to think anymore.</t>
+          <t>It's true that it feels good and that I'm flushed,
+but I don't have any room left to think anymore.</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6196,8 +6204,8 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>Even though Rurichiyo-chan is answering me, I can only
-give a half‑hearted reply.</t>
+          <t>Even though Rurichiyo-chan is answering me, I can
+only give a half‑hearted reply.</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -6427,8 +6435,8 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>「I-It's okay... you can't see anything; my shirt's hem
-is covering it...」</t>
+          <t>「I-It's okay... you can't see anything; my shirt's
+hem is covering it...」</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6580,7 +6588,8 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, just as I said, waves toward the girl.</t>
+          <t>Rurichiyo-chan, just as I said, waves toward the
+girl.</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6797,8 +6806,8 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>No matter how I try to stop, the horse keeps making my
-hips move and I can't help but keep going.</t>
+          <t>No matter how I try to stop, the horse keeps making
+my hips move and I can't help but keep going.</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6906,8 +6915,8 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>When my body lifted, with a wet, thrusting feeling the
-penis hit the soft place deep inside.</t>
+          <t>When my body lifted, with a wet, thrusting feeling
+the penis hit the soft place deep inside.</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -7015,8 +7024,8 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t>That tiny body must be feeling it even more than I am,
-and it sinks down toward me.</t>
+          <t>That tiny body must be feeling it even more than I
+am, and it sinks down toward me.</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -7201,8 +7210,8 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>Once again the horse jolts wildly, the tiny body drops
-and sinks even deeper.</t>
+          <t>Once again the horse jolts wildly, the tiny body
+drops and sinks even deeper.</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7528,8 +7537,8 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>「Fah, Oji-sama... Oji-sama！ Jeez... nn！ Geez... nnng！？
-Ah... haa...！」</t>
+          <t>「Fah, Oji-sama... Oji-sama！ Jeez... nn！ Geez...
+nnng！？ Ah... haa...！」</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7544,8 +7553,8 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t>A hot lump is rising up from deep inside, I'm about to
-come... I'm gonna cum！</t>
+          <t>A hot lump is rising up from deep inside, I'm about
+to come... I'm gonna cum！</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -7729,8 +7738,8 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama！ Oji-sa... ahhh, haa！ Uwaaah, ahhhh, ah, ah！
-Haaaah！」</t>
+          <t>「Oji-sama！ Oji-sa... ahhh, haa！ Uwaaah, ahhhh, ah,
+ah！ Haaaah！」</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -8053,8 +8062,8 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>I catch her properly and lean forward, bracing my body
-as well.</t>
+          <t>I catch her properly and lean forward, bracing my
+body as well.</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8129,8 +8138,8 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>Even after she came and her body went completely limp,
-it still wouldn't stop.</t>
+          <t>Even after she came and her body went completely
+limp, it still wouldn't stop.</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -8221,8 +8230,8 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>The up-and-down motion, as if to push me over the edge
-again, squeezes out the last of today's seed.</t>
+          <t>The up-and-down motion, as if to push me over the
+edge again, squeezes out the last of today's seed.</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -9071,9 +9080,9 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>Tucked the penis into Rurichiyo-chan's clothes and had
-her pull up her panties... She really managed that
-well.</t>
+          <t>Tucked the penis into Rurichiyo-chan's clothes and
+had her pull up her panties... She really managed
+that well.</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9088,8 +9097,8 @@
       </c>
       <c r="B561" s="1" t="inlineStr">
         <is>
-          <t>I can't hesitate in my moves, and I worked out a trick
-to get down so I'm in the horse's shadow...</t>
+          <t>I can't hesitate in my moves, and I worked out a
+trick to get down so I'm in the horse's shadow...</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -9560,7 +9569,8 @@
       </c>
       <c r="B592" s="1" t="inlineStr">
         <is>
-          <t>「Where on earth have you been? I was looking for you!」</t>
+          <t>「Where on earth have you been? I was looking for
+you!」</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -9787,8 +9797,8 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>...Since then, at Rurichiyo-chan's request, I rode the
-merry-go-round five times in a row...</t>
+          <t>...Since then, at Rurichiyo-chan's request, I rode
+the merry-go-round five times in a row...</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -9971,8 +9981,8 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>「That sounds great！ Janitor-sensei looks tired too, so
-let's do something relaxing and let it soothe us！」</t>
+          <t>「That sounds great！ Janitor-sensei looks tired too,
+so let's do something relaxing and let it soothe us！」</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -10017,9 +10027,9 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>There was nothing snide in Miru-chan's and Nono-chan's
-words, but since I'd just ridden it five times, I
-couldn't help but jump.</t>
+          <t>There was nothing snide in Miru-chan's and
+Nono-chan's words, but since I'd just ridden it five
+times, I couldn't help but jump.</t>
         </is>
       </c>
       <c r="C622" t="n">

--- a/processed_ruby_restored_xlsx/sc226_瑠璃８：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc226_瑠璃８：遊園地.ss.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -562,7 +562,7 @@
       <c r="B7" s="1" t="inlineStr">
         <is>
           <t>We were all together just a moment ago—how did this
-happen...?</t>
+happen...?"</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -578,7 +578,7 @@
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>When one of them bolts off, another kid follows, and
-then someone else runs after them to stop them...</t>
+then someone else runs after them to stop them..."</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -594,7 +594,7 @@
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Because someone is chasing someone else, when one
-takes off it's like dominos.</t>
+takes off it's like dominos."</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -610,7 +610,7 @@
       <c r="B10" s="1" t="inlineStr">
         <is>
           <t>I'd been watching them carefully, but I looked away
-for just a moment and finally we got separated.</t>
+for just a moment and finally we got separated."</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -626,7 +626,7 @@
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>So now, the only one left by my side is
-Rurichiyo-chan, who'd been staying quiet.</t>
+Rurichiyo-chan, who'd been staying quiet."</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>Maybe I'll try baiting her a little...</t>
+          <t>Maybe I'll try baiting them a little...</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>When I pull my body in close, a cute little sound
+          <t>When he pulls his body in close, a cute little sound
 immediately escapes her.</t>
         </is>
       </c>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>my penis swells in response to that voice, growing
+          <t>his penis swells in response to that voice, growing
 hard and large.</t>
         </is>
       </c>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>「N-no, n-no way！ What are you making me say...！?」</t>
+          <t>N-no, n-no way！ What are you making me say...！?</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>「Fufu...！」</t>
+          <t>Fufu...！</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3060,8 +3060,8 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>At the moment I reach for her panties, Rurichiyo-chan
-doesn't resist.</t>
+          <t>At the moment he reaches for her panties,
+Rurichiyo-chan doesn't resist.</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>Taking advantage of that, I quickly slid it down...</t>
+          <t>Taking advantage of that, he quickly slid it down...</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>I stroke her stomach from behind while rubbing my
+          <t>He strokes her stomach from behind while rubbing his
 penis against the area between her legs.</t>
         </is>
       </c>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>「Ah, that was close...」</t>
+          <t>Ah, that was close...</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>「Oh, come on, you hopeless Oji-sama…！」</t>
+          <t>Oh, come on, you hopeless Oji-sama…！</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>I gently pat her head.</t>
+          <t>I gently pat their head.</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>Right now I'm Rurichiyo-chan's prince.</t>
+          <t>Right now he's Rurichiyo-chan's prince.</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5402,7 +5402,7 @@
       <c r="B321" s="1" t="inlineStr">
         <is>
           <t>When wrapped in those gentle words, Rurichiyo-chan,
-settled in my arms, nods as if relieved.</t>
+settled in his arms, nods as if relieved.</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>「Hah！ Ahh！ Fuaa！ Nn！ Oji-sama... oji, sa, ahhh...！」</t>
+          <t>Hah！ Ahh！ Fuaa！ Nn！ Oji-sama... oji, sa, ahhh...！</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>「Haah, haah… Ahh！ Nn, yesss…！ Nnnh, nnngh… kufuuu…！」</t>
+          <t>Haah, haah… Ahh！ Nn, yesss…！ Nnnh, nnngh… kufuuu…！</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>「Waaah…！ Where… is it getting hot？」</t>
+          <t>Waaah…！ Where… is it getting hot？</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>「O- Oji-sama... what has happened...！？」</t>
+          <t>O- Oji-sama... what has happened...！？</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6435,8 +6435,8 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>「I-It's okay... you can't see anything; my shirt's
-hem is covering it...」</t>
+          <t>I-It's okay... you can't see anything; my shirt's hem
+is covering it...</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t>As I thought, since Rurichiyo-chan waved, it seems I
+          <t>As I thought, since Rurichiyo-chan waved, it seems he
 no longer finds it suspicious...</t>
         </is>
       </c>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>「Waaah... ah, ha！ Haa... n, nnu！」</t>
+          <t>Waaah... ah, ha！ Haa... n, nnu！</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ahh… I'm about to cum…！」</t>
+          <t>Ah, ahh… I」m about to cum…！</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t>「Haa... fuwaa！ I-I'm... I can't... anymore... aaah！」</t>
+          <t>Haa... fuwaa！ I-I'm... I can't... anymore... aaah！</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>「Ugh！ Aaah, ha！ Hah！」</t>
+          <t>Ugh！ Aaah, ha！ Hah！</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7707,8 +7707,8 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t>「Aaaaah！ It's coming...！ It's coming out！ Uaaaah！
-Aaaah！」</t>
+          <t>Aaaaah！ It's coming...！ It's coming out！ Uaaaah！
+Aaaah！</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7738,8 +7738,8 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama！ Oji-sa... ahhh, haa！ Uwaaah, ahhhh, ah,
-ah！ Haaaah！」</t>
+          <t>Oji-sama！ Oji-sa... ahhh, haa！ Uwaaah, ahhhh, ah, ah！
+Haaaah！</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -7815,8 +7815,8 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>「Hah！ Aahhh...！ Oji-sama... auh！ Amazing... it's
-amazing... nngh！」</t>
+          <t>Hah！ Aahhh...！ Oji-sama... auh！ Amazing... it's
+amazing... nngh！</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>Her vagina clamps down tight, squeezing hard from the
+          <t>My vagina clamps down tight, squeezing hard from the
 base.</t>
         </is>
       </c>
@@ -7894,8 +7894,8 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah！ If you do that much to me...！ I... again...
-again, aaah！」</t>
+          <t>Ah, ah！ If you do that much to me...！ I... again...
+again, aaah！</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -7925,8 +7925,8 @@
       </c>
       <c r="B484" s="1" t="inlineStr">
         <is>
-          <t>「Uah, ah！ No... not like that！ If you squeeze me like
-that—！ Uaaa, ahh！ Hah—haaah！」</t>
+          <t>Uah, ah！ No... not like that！ If you squeeze me like
+that—！ Uaaa, ahh！ Hah—haaah！</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>When I pulled my penis out, Rurichiyo-chan let out a
+          <t>When I pulled his penis out, Rurichiyo-chan let out a
 heartrending cry.</t>
         </is>
       </c>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... your panties are all soggy, huh...？」</t>
+          <t>Ugh... your panties are all soggy, huh...？</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>「...Well, leave me be for now, what should we ride
+          <t>「...Well, leave him be for now, what should we ride
 next？」</t>
         </is>
       </c>
@@ -9950,8 +9950,8 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>「Okay, okay, yoo-hoo！ Miru, I want to ride the
-merry-go-round next！」</t>
+          <t>Okay, okay, yoo-hoo！ Miru, I want to ride the
+merry-go-round next！</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>「Hehe... Is that all right...?」</t>
+          <t>Hehe... Is that all right...?</t>
         </is>
       </c>
       <c r="C624" t="n">
